--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -522,12 +522,16 @@
         <v>48.96</v>
       </c>
       <c r="I2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-22.22</v>
+      </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-10.88</v>
       </c>
     </row>
     <row r="3">
@@ -562,12 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.65</v>
+        <v>10.95</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>2.82</v>
+      </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -602,12 +608,16 @@
         <v>6.54</v>
       </c>
       <c r="I4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>1.93</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-11.47</v>
+      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="5">
@@ -642,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.95</v>
+        <v>10.84</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>2.82</v>
+        <v>1.78</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4">
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.84</v>
+        <v>11.83</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1.78</v>
+        <v>11.08</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="4">
@@ -642,20 +642,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>44.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -692,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11.83</v>
+        <v>11.87</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>11.08</v>
+        <v>11.46</v>
       </c>
       <c r="L3" t="n">
-        <v>4.72</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="4">
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11.87</v>
+        <v>12.18</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>11.46</v>
+        <v>14.37</v>
       </c>
       <c r="L3" t="n">
-        <v>4.88</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="4">
@@ -652,14 +652,14 @@
         <v>44.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>12.6</v>
+        <v>19.63</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>12.18</v>
+        <v>12.05</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>14.37</v>
+        <v>13.15</v>
       </c>
       <c r="L3" t="n">
-        <v>6.12</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +642,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -652,14 +652,16 @@
         <v>44.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>0.42</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.35</v>
+      </c>
       <c r="K5" t="n">
-        <v>19.63</v>
+        <v>23.15</v>
       </c>
       <c r="L5" t="n">
-        <v>2.78</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="6">
@@ -684,17 +686,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>48.09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/rocket_journal.xlsx
+++ b/rocket_journal.xlsx
@@ -566,14 +566,14 @@
         <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>12.05</v>
+        <v>11.9</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13.15</v>
+        <v>11.74</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -686,7 +686,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -696,12 +696,16 @@
         <v>48.09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>0.21</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-7.05</v>
+      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
     </row>
   </sheetData>
